--- a/files/Super_Rugby_upcoming_projections.xlsx
+++ b/files/Super_Rugby_upcoming_projections.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t xml:space="preserve">model_mode</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time</t>
   </si>
   <si>
     <t xml:space="preserve">home_team</t>
@@ -23,10 +26,79 @@
     <t xml:space="preserve">away_team</t>
   </si>
   <si>
+    <t xml:space="preserve">forecast_rain_mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
     <t xml:space="preserve">home_lineup_flag</t>
   </si>
   <si>
     <t xml:space="preserve">away_lineup_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market_Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projection_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currentpar_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currentpar_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_home_line_ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_total_ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">systemic_margin_adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">systemic_total_adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusaders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurricanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">domestic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiefs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brumbies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">international</t>
   </si>
 </sst>
 </file>
@@ -34,11 +106,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,8 +139,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -354,28 +434,512 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.7099998053726" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.70999982483533" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="5.7099999026863" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="5.7099999026863" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="9.70999982483533" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10.7099998053726" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="5.7099999026863" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.7099997469844" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="20.7099996107452" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="18.7099996496707" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="14.7099997275216" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="13.7099997469844" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9.70999982483533" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="19.7099996302079" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="18.7099996496707" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-12.73</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-17.46</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>-12.73</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>-17.46</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>-8.03</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>-8.03</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
